--- a/sensitivity_results/legacy/multiconcept/experiment_results_grouped_patchedin.xlsx
+++ b/sensitivity_results/legacy/multiconcept/experiment_results_grouped_patchedin.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srikant1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EF64D7C-18B0-4164-BCEE-59CF5858BF49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{494C5FE2-06BA-458A-BE16-93B68BD70C1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="8" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="8" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="inception_v3_deer" sheetId="1" r:id="rId1"/>
@@ -28,6 +28,7 @@
     <sheet name="vgg16_deer" sheetId="13" r:id="rId13"/>
     <sheet name="vgg16_horse" sheetId="14" r:id="rId14"/>
     <sheet name="vgg16_zebra" sheetId="15" r:id="rId15"/>
+    <sheet name="Sheet1" sheetId="16" r:id="rId16"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">inception_v3_deer!$A$1:$O$49</definedName>
@@ -64,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5580" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5583" uniqueCount="33">
   <si>
     <t>Precision</t>
   </si>
@@ -155,6 +156,15 @@
   <si>
     <t>vgg16</t>
   </si>
+  <si>
+    <t>Deer with Horse Background</t>
+  </si>
+  <si>
+    <t>Deer with Horse Coat</t>
+  </si>
+  <si>
+    <t>Zebra with Horse coat</t>
+  </si>
 </sst>
 </file>
 
@@ -229,6 +239,187 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>467641</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>58017</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{537BA2AB-87CF-60E6-DEFA-CA020823254D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="6563641" cy="6211167"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>381989</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>143451</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{59B24D39-0EE5-D4D3-677E-20A222EACE62}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7315200" y="0"/>
+          <a:ext cx="7087589" cy="4124901"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>543256</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>133672</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{482F1137-377C-A833-2610-8F750015B579}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7315200" y="5067300"/>
+          <a:ext cx="2372056" cy="2305372"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>86503</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>76716</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A4611C0C-F4A2-91AA-E65E-3EEF805005B4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10972800" y="5067300"/>
+          <a:ext cx="5572903" cy="3696216"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -18369,6 +18560,32 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FAF9440-7221-48EF-AFF0-0C031FB2569C}">
+  <dimension ref="A26:U50"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="26" spans="14:14" x14ac:dyDescent="0.35">
+      <c r="N26" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="50" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U50" t="s">
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr filterMode="1"/>
